--- a/bjt-front/bjt-product-system/generated_sql_imports/name统一.xlsx
+++ b/bjt-front/bjt-product-system/generated_sql_imports/name统一.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160"/>
+    <workbookView windowWidth="31900" windowHeight="17260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1408,7 +1408,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2839,7 +2839,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" ht="17" spans="1:6">
+    <row r="35" ht="16.8" spans="1:6">
       <c r="A35" s="16"/>
       <c r="B35" s="14" t="s">
         <v>108</v>
@@ -3061,7 +3061,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" ht="17" spans="1:6">
+    <row r="48" ht="16.8" spans="1:6">
       <c r="A48" s="20"/>
       <c r="B48" s="14" t="s">
         <v>143</v>
